--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -6507,11 +6507,7 @@
           <t>Yes — counted directly, see the counts column.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3501 decisions extracted, of which 2385 workers compensation (2 of 3,503 citations failed extraction)</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6561,7 +6557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6600,6 +6596,11 @@
           <t>lesson</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>footnote</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6637,6 +6638,7 @@
           <t>Correlated measurement error is more dangerous than noise. Noise attenuates an estimate; correlated error invents a finding. Provenance discipline - recording WHERE a value came from, and being able to read the evidence back - is what makes this class of error findable at all.</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6646,17 +6648,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The rule-side outcome classifier put the worker's success rate at 75.2% across the full corpus. The LLM pass, on a 100-case sample, put it at 66%, finding roughly twice as much 'mixed' (11% vs 5.2%).</t>
+          <t>Over the full corpus the rule-side outcome classifier puts the worker's success rate at 75.2% and the LLM pass at 72.3%, with the LLM finding roughly twice as much 'mixed' (10.7% vs 5.2%). The two disagree on 259 cases, 10.9% of the corpus - and 'mixed' appears on one side or the other in 92.7% of them.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Neither is wrong. They disagree about whether a partial success - the worker wins on some heads and loses on others - counts as a win.</t>
+          <t>Neither is wrong. They disagree about whether a partial success - the worker wins on some heads and loses on others - counts as a win. The disagreement set and the partial-success population are effectively the same object.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>The choice moves the headline base rate by about nine points. If that base rate feeds a remuneration or conduct metric, money attaches to the definition, and a scheme participant will contest the definition of 'loss' long before it contests any model built on top of it.</t>
+          <t>Counting 'mixed' as a win rather than a loss moves the headline base rate by 10.7 points, and it does not move it evenly: Permanent Impairment is 30.1% of the disagreement set against 15.8% of the corpus. If that base rate feeds a remuneration or conduct metric, money attaches to the definition, and a scheme participant will contest the definition of 'loss' long before it contests any model built on top of it.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6674,6 +6676,87 @@
           <t>Definitional risk is quantifiable and belongs in the metric design, not in a footnote. Report the base rate under both definitions.</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The earlier version of this example quoted 66% and a nine-point swing, taken from the 100-case sample. Re-derived over the full corpus the figures are 72.3% and 10.7 points. The sample was stratified on gender and WPI presence and was faithful on both, but drifted on dispute type, which nobody had stratified on - see 'The sample that was representative of the wrong things'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Partial denial: when a category disagreement is a category error</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>liability_posture was extracted twice, by a text rule and by the LLM, into a binary: was liability itself in issue, or was it admitted and only entitlement disputed? The two methods disagreed on 711 of 2,385 cases (29.8%), and the disagreement was directional 4:1 - 494 cases where the LLM read denial and the rule read quantum-only, against 129 the other way.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Neither extractor was misreading. In the dominant cell a consequential condition is claimed in 47.8% of cases against a 25.6% base rate, and the rule is quoting explicit concession language in 406 of the 494. Both are reading real words on the page: liability WAS admitted for the primary injury, and it WAS denied for the consequential condition, the treatment, or the impairment head. The category had no value for that, so each method rounded to a different side.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This is a gaming channel, not just a data-quality defect. Under the binary, an insurer that accepts the injury but denies every consequential condition, treatment and impairment head reads as 'quantum only' - the cooperative category. Deny in part, never in whole, and a conduct metric built on this field cannot see it. The field sits close to the metric's target concept, so the error propagates rather than washing out.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>The cross-check was nearly suppressed: the marginals almost match (denied 46 v 49, quantum 47 v 40, procedural 7 v 11), so the field looked fine at the aggregate. Similar marginals with case-level disagreement is exactly the signature worth investigating, and the cross-tab - not the marginals - showed the direction.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Do not adjudicate a winner. Draw a reference set FROM the disagreement cells (25/12/13 across the three, deliberately non-proportional), offer the labeller the third value the schema cannot return, and cross the dominant cell on the hypothesised mechanism and on rule strength so 'the category is wrong' and 'the rule is weak' can be told apart. If it holds, liability_denied_in_part becomes a third value.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>When two competent methods disagree about a category and both can quote the text, suspect the category before you suspect the methods. A binary that cannot express a real state of the world does not merely lose information - it creates a channel for anyone who benefits from occupying that state.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>The sample that was representative of the wrong things</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A 100-case sample, drawn stratified on claimant gender and WPI presence, put liability_denied at 49%. The full corpus put it at 63%. Every figure quoted from that sample - including a worked example in this very sheet - inherited the gap.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The stratification did its job: sample WPI presence 5.0% against a corpus 4.9%, male 59% against 60%. But nothing was stratified on dispute type, and dispute type drifted - Procedural 11% against 6.5%, Liability Dispute 24% against 28% - across categories whose denial rates span 8.3% to 97.8%. Re-weighting the corpus to the sample's dispute mix recovers 3 of the 14 points; the rest is an unlucky draw at roughly 2.2 standard errors.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A sample stratified on two variables is UNSTRATIFIED on every other one, and the ones that bite are whichever happen to correlate with the outcome. Nothing about the sample looked wrong: the variables anyone had thought to check reproduced the corpus almost exactly.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>The same figure was computed over the full corpus and did not match. The sample's own cases were then re-scored in the full run and gave 49% again, which ruled out run-to-run instability and left composition and luck.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Re-derive every sample-quoted figure from the full corpus once the full run exists. Keep hand-labelled samples for what only a human can supply - a label - and never for a base rate.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Stratification buys representativeness on the variables you named and nothing else. Check the marginals that matter for the CONCLUSION, not the ones you happened to stratify on.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Counting 'mixed' as a win rather than a loss moves the headline base rate by 10.7 points, and it does not move it evenly: Permanent Impairment is 30.1% of the disagreement set against 15.8% of the corpus. If that base rate feeds a remuneration or conduct metric, money attaches to the definition, and a scheme participant will contest the definition of 'loss' long before it contests any model built on top of it.</t>
+          <t>Counting 'mixed' as a win rather than a loss moves the headline base rate by 10.7 points, and - see the definitional_metric_shift sheet - it does not move it evenly: 23.3 points on Permanent Impairment against 4.7 on Death Benefit. So the definition does not merely shift a number, it REDISTRIBUTES penalty between providers according to their book. A participant heavy in impairment matters is both disadvantaged by the base rate and most exposed to the definitional choice; the two compound. Whoever sets the definition is making a distributive decision wearing technical clothes, and a scheme participant will contest it long before it contests any model built on top of it.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6013,6 +6013,286 @@
       <c r="F192" t="inlineStr">
         <is>
           <t>Whether this row tripped any quality flag defined here. Replaces the pipeline flag, which cannot see an empty WPI in a permanent-impairment matter or a binary field where two independent extractors disagree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>denial_scope</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>semicolon-separated: primary_injury / consequential_condition / specific_treatment / impairment_head / weekly_entitlement / work_capacity / nothing_denied / not_stated</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Every head liability was denied for. This is what makes partial denial COUNTABLE: under the liability_posture binary, denying every consequential condition while accepting the injury reads as the cooperative 'quantum only' category.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>denial_scope_evidence</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Verbatim quote showing what was denied. Empty where nothing was denied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>heads_claimed</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0 = undeterminable</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>How many distinct heads of relief the worker pressed for decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>heads_succeeded</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>&lt;= heads_claimed</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>How many of those heads the worker won. Cross-checked against heads_claimed; a violation sets conduct_status to 'heads_inconsistent' rather than publishing the value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>conduct_finding</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>criticism_made / considered_not_criticised / not_addressed</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Whether the Member remarked on the INSURER's conduct of the claim. Three-way on purpose: silence and express approval are opposite evidence for convergent validity and identical under a boolean. Losing is not criticism -- an insurer can lose with impeccable conduct on fresh medical evidence, or win having handled the matter badly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>conduct_scope</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>semicolon-separated: reasons_adequacy / timeliness / investigation_proportionality / surveillance / failure_to_consider_evidence / defective_notice / other_conduct</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>What was criticised, in SIRA Standards of Practice terms. Deliberately the regulator's vocabulary: it lets the metric be validated against the actual standard rather than against generalised judicial disapproval, and absorbs surveillance and defective notices as scope values rather than separate booleans.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>conduct_evidence</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Verbatim quote of the Member's remark on conduct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>claimant_success_degree</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0.0-1.0, null if heads_claimed = 0</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>heads_succeeded / heads_claimed. Turns the definitional question from a two-point comparison into a sensitivity curve: 'mixed' currently covers winning four heads of five and one of five alike.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>conduct_status</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>ok / not run / heads_inconsistent / error text</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Whether the second pass ran. Distinguishes 'not run' from 'ran and found nothing', for the same reason conduct_finding is three-way.</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6757,6 +7037,44 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Half the budget went to two fields</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>The full run cost $115.37 over 5,044 calls for 2,385 decisions. Only 2,385 of those calls were the extraction. The other 2,659 were the stability gate: a best-of-three vote on primary_injury and legal_complexity, the two fields measured at 91% run-to-run stability.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nothing was wrong with the gate. What was wrong is that it was a default rather than a decision. Each vote re-sends the ENTIRE decision text - mean 50.7k characters - to re-answer two fields, so the gate pays full input price for a fraction of the schema and accounts for roughly half the run.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Input tokens are about 69% of this workload's cost, so architecture choices that re-send the source dominate the bill, and they are invisible in a per-call average. 'Stabilise the two shakiest fields' sounds free and costs $50. The same reasoning decided the conduct fields: an additive second pass keyed separately from the main schema costs about $42, where re-running everything to add them would have cost $115 - and would have moved every figure already published in this workbook.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dividing the run's call count by the corpus size gave 2.11 passes' worth of text for one pass of output, which does not reconcile until you notice the gate is re-sending everything.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Price the architecture, not just the model. Ask what each mechanism re-sends, how often, and for how much of the schema; then decide whether the quality it buys is worth that, and record the decision either way.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cost lives in the architecture as much as the price list. Its companion lesson - estimate token cost from the corpus LENGTH DISTRIBUTION, never from a small-sample per-case average - is about getting the unit price right; this one is about knowing how many units your design quietly ordered.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -5955,12 +5955,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>review_flags</t>
+          <t>conduct_status</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>conduct</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5970,29 +5970,29 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>semicolon-separated</t>
+          <t>ok / not run / heads_inconsistent / error text</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
+          <t>Whether the second pass ran. Distinguishes 'not run' from 'ran and found nothing', for the same reason conduct_finding is three-way.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>needs_review_derived</t>
+          <t>denial_scope</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>conduct</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6002,24 +6002,24 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>llm_second_pass</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Yes / No</t>
+          <t>semicolon-separated: primary_injury / consequential_condition / specific_treatment / impairment_head / weekly_entitlement / work_capacity / nothing_denied / not_stated</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Whether this row tripped any quality flag defined here. Replaces the pipeline flag, which cannot see an empty WPI in a permanent-impairment matter or a binary field where two independent extractors disagree.</t>
+          <t>Every head liability was denied for. This is what makes partial denial COUNTABLE: under the liability_posture binary, denying every consequential condition while accepting the injury reads as the cooperative 'quantum only' category.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>denial_scope</t>
+          <t>denial_scope_evidence</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6037,21 +6037,17 @@
           <t>llm_second_pass</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>semicolon-separated: primary_injury / consequential_condition / specific_treatment / impairment_head / weekly_entitlement / work_capacity / nothing_denied / not_stated</t>
-        </is>
-      </c>
+      <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Every head liability was denied for. This is what makes partial denial COUNTABLE: under the liability_posture binary, denying every consequential condition while accepting the injury reads as the cooperative 'quantum only' category.</t>
+          <t>Verbatim quote showing what was denied. Empty where nothing was denied.</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>denial_scope_evidence</t>
+          <t>heads_claimed</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6061,7 +6057,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -6069,17 +6065,21 @@
           <t>llm_second_pass</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0 = undeterminable</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Verbatim quote showing what was denied. Empty where nothing was denied.</t>
+          <t>How many distinct heads of relief the worker pressed for decision.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>heads_claimed</t>
+          <t>heads_succeeded</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6099,19 +6099,19 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>0 = undeterminable</t>
+          <t>&lt;= heads_claimed</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>How many distinct heads of relief the worker pressed for decision.</t>
+          <t>How many of those heads the worker won. Cross-checked against heads_claimed; a violation sets conduct_status to 'heads_inconsistent' rather than publishing the value.</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>heads_succeeded</t>
+          <t>conduct_finding</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6131,19 +6131,19 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>&lt;= heads_claimed</t>
+          <t>criticism_made / considered_not_criticised / not_addressed</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>How many of those heads the worker won. Cross-checked against heads_claimed; a violation sets conduct_status to 'heads_inconsistent' rather than publishing the value.</t>
+          <t>Whether the Member remarked on the INSURER's conduct of the claim. Three-way on purpose: silence and express approval are opposite evidence for convergent validity and identical under a boolean. Losing is not criticism -- an insurer can lose with impeccable conduct on fresh medical evidence, or win having handled the matter badly.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>conduct_finding</t>
+          <t>conduct_scope</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6163,19 +6163,19 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>criticism_made / considered_not_criticised / not_addressed</t>
+          <t>semicolon-separated: reasons_adequacy / timeliness / investigation_proportionality / surveillance / failure_to_consider_evidence / defective_notice / other_conduct</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Whether the Member remarked on the INSURER's conduct of the claim. Three-way on purpose: silence and express approval are opposite evidence for convergent validity and identical under a boolean. Losing is not criticism -- an insurer can lose with impeccable conduct on fresh medical evidence, or win having handled the matter badly.</t>
+          <t>What was criticised, in SIRA Standards of Practice terms. Deliberately the regulator's vocabulary: it lets the metric be validated against the actual standard rather than against generalised judicial disapproval, and absorbs surveillance and defective notices as scope values rather than separate booleans.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>conduct_scope</t>
+          <t>conduct_evidence</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6193,21 +6193,17 @@
           <t>llm_second_pass</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>semicolon-separated: reasons_adequacy / timeliness / investigation_proportionality / surveillance / failure_to_consider_evidence / defective_notice / other_conduct</t>
-        </is>
-      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>What was criticised, in SIRA Standards of Practice terms. Deliberately the regulator's vocabulary: it lets the metric be validated against the actual standard rather than against generalised judicial disapproval, and absorbs surveillance and defective notices as scope values rather than separate booleans.</t>
+          <t>Verbatim quote of the Member's remark on conduct.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>conduct_evidence</t>
+          <t>claimant_success_degree</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6217,35 +6213,39 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>llm_second_pass</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0.0-1.0, null if heads_claimed = 0</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Verbatim quote of the Member's remark on conduct.</t>
+          <t>heads_succeeded / heads_claimed. Turns the definitional question from a two-point comparison into a sensitivity curve: 'mixed' currently covers winning four heads of five and one of five alike.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>claimant_success_degree</t>
+          <t>review_flags</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>conduct</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -6255,24 +6255,24 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0.0-1.0, null if heads_claimed = 0</t>
+          <t>semicolon-separated</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>heads_succeeded / heads_claimed. Turns the definitional question from a two-point comparison into a sensitivity curve: 'mixed' currently covers winning four heads of five and one of five alike.</t>
+          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>conduct_status</t>
+          <t>needs_review_derived</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>conduct</t>
+          <t>review</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>ok / not run / heads_inconsistent / error text</t>
+          <t>Yes / No</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Whether the second pass ran. Distinguishes 'not run' from 'ran and found nothing', for the same reason conduct_finding is three-way.</t>
+          <t>Whether this row tripped any quality flag defined here. Replaces the pipeline flag, which cannot see an empty WPI in a permanent-impairment matter or a binary field where two independent extractors disagree.</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,11 @@
           <t>Yes — counted directly, see the counts column.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3501 decisions extracted, of which 2385 workers compensation (2 of 3,503 citations failed extraction)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -6136,7 +6136,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Whether the Member remarked on the INSURER's conduct of the claim. Three-way on purpose: silence and express approval are opposite evidence for convergent validity and identical under a boolean. Losing is not criticism -- an insurer can lose with impeccable conduct on fresh medical evidence, or win having handled the matter badly.</t>
+          <t>Whether the Member remarked on the INSURER's conduct of the claim. Three-way on purpose: silence and express approval are opposite evidence for convergent validity and identical under a boolean. Losing is not criticism -- an insurer can lose with impeccable conduct on fresh medical evidence, or win having handled the matter badly. MEASURED: criticism_made 5.7%, considered_not_criticised 2.1%, not_addressed 92.1%. Claimant success runs 87.6% / 62.7% / 71.6% across those three, so the arms fall on BOTH sides of baseline. ENDOGENEITY CAVEAT, which anyone using this as a validation target must state: the conduct remark and the outcome are recorded in the same document by the same person, so criticism is partly downstream of the finding rather than independent of it. The considered_not_criticised arm is a partial answer -- pure endogeneity would not place it BELOW the not_addressed baseline -- but it is a mitigation, not a refutation.</t>
         </is>
       </c>
     </row>
@@ -6787,11 +6787,7 @@
           <t>Yes — counted directly, see the counts column.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3501 decisions extracted, of which 2385 workers compensation (2 of 3,503 citations failed extraction)</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6841,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6984,7 +6980,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>This is a gaming channel, not just a data-quality defect. Under the binary, an insurer that accepts the injury but denies every consequential condition, treatment and impairment head reads as 'quantum only' - the cooperative category. Deny in part, never in whole, and a conduct metric built on this field cannot see it. The field sits close to the metric's target concept, so the error propagates rather than washing out.</t>
+          <t>This is a gaming channel, not just a data-quality defect, and it is now MEASURED rather than inferred. Extracting what was denied (denial_scope) shows that of the 748 cases the binary reads as 'quantum only' - the cooperative category - 51.3% carry a recorded denial of a consequential condition, a treatment or an impairment head, and 49.1% denied something without denying the primary injury. Corpus-wide the pattern covers 828 cases, 34.7%. Deny in part, never in whole, and a conduct metric built on this field cannot see it: half of what it scores as cooperative contains a denial. The field sits close to the metric's target concept, so the error propagates rather than washing out.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7002,7 +6998,11 @@
           <t>When two competent methods disagree about a category and both can quote the text, suspect the category before you suspect the methods. A binary that cannot express a real state of the world does not merely lose information - it creates a channel for anyone who benefits from occupying that state.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A hypothesis died here and it is worth keeping the corpse. The prediction was that partial denial would be CONCENTRATED in the 494-case disagreement cell, and it is not: inside that cell primary injury is denied 59.1% of the time - the LLM's reading backed against the rule's, so rule weakness - and the partial-not-primary signature is 36.6% against a 32.0% baseline on rows where the methods AGREE. Partial denial is a property of the category corpus-wide, not of where the two methods disagree. The finding survived losing its mechanism, and got larger: the channel does not need the disagreement to exist.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7079,6 +7079,44 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>The field that was specified at the wrong granularity</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>claimant_success_degree was defined as heads_succeeded / heads_claimed, to turn the definitional question from a two-point comparison into a sensitivity curve. Extracted over the full corpus at a cost of $46, it came back flat: 64.4% of decisions press a SINGLE head, so the ratio can only be 0 or 1, and 154 of the 255 'mixed' decisions scored 1.0.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>The specification assumed 'mixed' means winning some heads and losing others. In workers compensation it usually means partial success WITHIN one head - a reduced period of weekly payments, some treatment approved and some refused. The field measured a real quantity accurately; it was the wrong quantity.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Nothing in the schema, the prompt or the validation would have caught this. The field is well defined, the model answered it correctly, and every value is defensible. It fails only against its PURPOSE, and that failure is invisible until you look at the distribution - where it is obvious at a glance, and would have been obvious in 100 cases for about $2 rather than 2,385 for $46.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cross-tabulating the new field against the outcome it was meant to refine. A field that disagrees with the thing it is supposed to be a finer-grained version of is either wrong or measuring something else.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pilot the DISTRIBUTION of a derived field before buying the full pass, and pilot it with repeated votes where the field is a judgment rather than a fact. The replacement here - an ordinal for within-head partiality - carries the larger risk, because degree judgments are where run-to-run variance concentrates and an unstable ordinal yields a sensitivity curve made of noise.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Specification errors are invisible in the schema and obvious in the histogram. Validation asks whether the field is right; only the distribution asks whether it is USEFUL, and the two come apart exactly when a field is derived rather than observed.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6235,12 +6235,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>review_flags</t>
+          <t>relief_status</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>conduct</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6250,47 +6250,231 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>semicolon-separated</t>
+          <t>ok / not run / error text</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
+          <t>Whether the relief pass ran.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>relief_granted_degree</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>fully_granted / substantially_granted / partly_granted / minimally_granted / refused / not_determinable</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>How much of what the worker PRESSED was granted, counting partial success within a head. Replaces the heads_succeeded/heads_claimed ratio, which measured the wrong granularity: 64.4% of the corpus presses a single head, so the ratio could only be 0 or 1 and scored 60% of 'mixed' decisions at a perfect 1.0. This is the field that makes the definitional question a sensitivity curve rather than a two-point comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>relief_granted_evidence</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Verbatim quote from the orders supporting the degree.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>relief_agreement</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>single_vote / unanimous / majority / no_majority / not_run</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>How the delivered degree was arrived at. Re-voting is TARGETED at the middle three categories, where the sensitivity threshold slides, so an extreme carrying 'single_vote' is not less trustworthy than a re-voted middle case -- it was never in doubt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>relief_votes</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>comma-separated</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Every vote cast, keyed internally by seed so the production vote and the pilot's first vote (which share a seed) cannot be counted twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>relief_stability</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>conduct</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Records that this field is SINGLE-VOTE. Piloted at 89% unanimous over 3 votes on 100 cases, against 91% on the gated fields. Gating was declined deliberately: the field feeds a sensitivity curve, where a label moving one adjacent step blurs the line, rather than a cohort assignment, where it would relocate a case between analysis populations. Treat roughly 11% of values as soft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>review_flags</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>semicolon-separated</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>needs_review_derived</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F207" t="inlineStr">
         <is>
           <t>Whether this row tripped any quality flag defined here. Replaces the pipeline flag, which cannot see an empty WPI in a permanent-impairment matter or a binary field where two independent extractors disagree.</t>
         </is>
@@ -6837,7 +7021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7078,7 +7262,11 @@
           <t>Cost lives in the architecture as much as the price list. Its companion lesson - estimate token cost from the corpus LENGTH DISTRIBUTION, never from a small-sample per-case average - is about getting the unit price right; this one is about knowing how many units your design quietly ordered.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>A third miss, from a mechanism neither of the first two covers. The relief pass was costed at $28 from the pilot's $0.0118/call and came in at $39.50, $0.0166/call. The pilot cast THREE votes per case on the same prompt, so two in every three of its calls hit the provider's prompt cache at a tenth of the input price. Its per-call average was therefore structurally cheaper than any single-vote pass could be. Note the shape: this is the representative-of-the-wrong-things error applied to COST rather than to a base rate. A sample can be unrepresentative in its unit economics as well as in its population, and repeated-call designs are exactly where that bites.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -7117,6 +7305,82 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>The bug whose symptom was reassurance</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>The relief ordinal is delivered by a single production vote and re-voted on the middle categories. Combining the delivered value with the re-votes by appending them to a list looks obviously correct. It is not: the production pass and the pilot's first vote use the SAME seed, so on the 100 pilot cases one opinion would have been counted twice.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>A duplicated answer always agrees with itself. Those cases would have reported 'unanimous' on the strength of a single opinion - and they are precisely the cases the pilot used to decide the field was stable enough to buy.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Look at the symptom. Every other failure in this set announced itself with an anomaly that INVITED a check: a 17-point gap between sample and corpus, a distribution flat at 1.0, a middle-category share slightly too high. This one's symptom is a HIGHER STABILITY NUMBER. It does not merely fail to invite investigation, it actively discourages it, because nobody audits a reassuring result. Diab at least produced a profile that a domain expert might have squinted at; a stability figure of 95% instead of 89% would have been quietly welcomed by everyone.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>From a fact about the CODE - that two call sites share a seed constant - not from a fact about the data. No amount of looking at the output would have surfaced it, because the output would have looked better than the truth.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Key votes by seed rather than accumulating them, so the same opinion cannot vote twice, and assert it in a test that fails if the collection order changes.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A number that is too good never prompts anyone to look. Any check that fires only when something seems wrong is structurally incapable of catching errors whose symptom is that things seem right.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Three species of wrong number, and the residual none of them catch</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>The failures in this build are not all the same kind of thing, and sorting them is what makes the defences selectable rather than a checklist. (1) SIGNABLE BIAS - the pilot's records[:100] draw. Once the mechanism is known the direction is known. (2) UNSIGNABLE BIAS - the Diab contamination and the sample's dispute-type drift. Plausibility gives no clue which way the error runs. (3) WRONG CONSTRUCT - the heads_succeeded/heads_claimed ratio. Not a biased estimate at all: the measure does not measure the thing.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Each species defeats the defences suited to the others. Standardising does nothing for an error whose direction you cannot sign. A second extractor is the only way to find contamination - and is exactly what fails against a wrong construct, because a second measure of the same wrong construct agrees with the first perfectly. Debiasing a wrong construct is not possible at all; only replacement is.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The three map onto three defences this build actually used, and each was used on the right species: standardise it (re-weighting the corpus to the sample's dispute mix, 63.0% -&gt; 59.8%); check provenance against an independent source (stripping citation context to find NRMA was a case name); look at the DISTRIBUTION before trusting the field (the pilot histogram, which would have shown 64.4% single-head immediately).</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Each by chasing an anomaly. That is the pattern - and the problem.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Match the defence to the species rather than running all three as ritual. But note what the taxonomy exposes: all three defences are TRIGGERED BY SUSPICION. Something has to look wrong first. So build at least one check that runs whether or not anything looks off - a test that fails on a duplicated vote, a provenance column that must be populated, an assertion that a field's coverage is what it was last run - because those are the only checks that reach the errors nobody would think to investigate.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>The residual risk after every suspicion-triggered defence lives entirely in results that look right. That is not a gap in diligence, it is a structural property of diligence, and the only answer is checks that do not wait to be motivated.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -6292,7 +6292,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>How much of what the worker PRESSED was granted, counting partial success within a head. Replaces the heads_succeeded/heads_claimed ratio, which measured the wrong granularity: 64.4% of the corpus presses a single head, so the ratio could only be 0 or 1 and scored 60% of 'mixed' decisions at a perfect 1.0. This is the field that makes the definitional question a sensitivity curve rather than a two-point comparison.</t>
+          <t>SCOPE: this field draws the definitional sensitivity CURVE. It is not an input to the metric, which stays count-based (the insurer loses or does not). Using it only for the curve is what makes an ~11% one-step labelling error tolerable: it smears the curve rather than relocating cases between outcome categories, so no re-vote was bought. STATED LIMITATION, which this field measures and the count-based metric cannot see: 305 of the 1,725 decisions scored as a claimant win -- 17.7% -- were granted LESS than fully (substantially 174, partly 118, minimally 13). The metric treats full recovery and minimal recovery as the same win, and this is the size of that. Report it; do not build it in. How much of what the worker PRESSED was granted, counting partial success within a head. Replaces the heads_succeeded/heads_claimed ratio, which measured the wrong granularity: 64.4% of the corpus presses a single head, so the ratio could only be 0 or 1 and scored 60% of 'mixed' decisions at a perfect 1.0. This is the field that makes the definitional question a sensitivity curve rather than a two-point comparison.</t>
         </is>
       </c>
     </row>

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F207"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6203,17 +6203,17 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>claimant_success_degree</t>
+          <t>liability_posture_3v</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>conduct</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -6223,19 +6223,19 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>0.0-1.0, null if heads_claimed = 0</t>
+          <t>liability_denied / liability_denied_in_part / quantum_or_entitlement_only / not_applicable_procedural / not_stated</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>heads_succeeded / heads_claimed. Turns the definitional question from a two-point comparison into a sensitivity curve: 'mixed' currently covers winning four heads of five and one of five alike.</t>
+          <t>Three-value posture, DERIVED from denial_scope, not extracted: primary_injury denied -&gt; liability_denied; nothing_denied -&gt; quantum_or_entitlement_only; anything else denied -&gt; liability_denied_in_part. Deterministic, so it cannot drift between runs and cost nothing. STRUCTURAL not legal: strictly only a denied consequential condition denies liability, while treatment, impairment head, weekly entitlement and work capacity are denials of entitlements flowing from accepted liability. The structural reading is used because the metric measures conduct, not pleading - a provider that accepts every injury and denies every weekly payment is not cooperative. 1,000 matters (41.9%) are in_part, and 514 of the 748 the binary called quantum_or_entitlement_only (68.7%) move there. The original liability_posture column is UNCHANGED beside it, so figures keyed to the binary stay checkable. INHERITS denial_scope's accuracy completely: denial_scope is single-source with no rule cross-check, and this derivation makes it load-bearing.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>relief_status</t>
+          <t>claimant_success_degree</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6245,29 +6245,29 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>float</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>audit</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ok / not run / error text</t>
+          <t>0.0-1.0, null if heads_claimed = 0</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Whether the relief pass ran.</t>
+          <t>heads_succeeded / heads_claimed. Turns the definitional question from a two-point comparison into a sensitivity curve: 'mixed' currently covers winning four heads of five and one of five alike.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>relief_granted_degree</t>
+          <t>relief_status</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6282,24 +6282,24 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>llm_second_pass</t>
+          <t>audit</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>fully_granted / substantially_granted / partly_granted / minimally_granted / refused / not_determinable</t>
+          <t>ok / not run / error text</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SCOPE: this field draws the definitional sensitivity CURVE. It is not an input to the metric, which stays count-based (the insurer loses or does not). Using it only for the curve is what makes an ~11% one-step labelling error tolerable: it smears the curve rather than relocating cases between outcome categories, so no re-vote was bought. STATED LIMITATION, which this field measures and the count-based metric cannot see: 305 of the 1,725 decisions scored as a claimant win -- 17.7% -- were granted LESS than fully (substantially 174, partly 118, minimally 13). The metric treats full recovery and minimal recovery as the same win, and this is the size of that. Report it; do not build it in. How much of what the worker PRESSED was granted, counting partial success within a head. Replaces the heads_succeeded/heads_claimed ratio, which measured the wrong granularity: 64.4% of the corpus presses a single head, so the ratio could only be 0 or 1 and scored 60% of 'mixed' decisions at a perfect 1.0. This is the field that makes the definitional question a sensitivity curve rather than a two-point comparison.</t>
+          <t>Whether the relief pass ran.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>relief_granted_evidence</t>
+          <t>relief_granted_degree</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6317,17 +6317,21 @@
           <t>llm_second_pass</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>fully_granted / substantially_granted / partly_granted / minimally_granted / refused / not_determinable</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Verbatim quote from the orders supporting the degree.</t>
+          <t>SCOPE: this field draws the definitional sensitivity CURVE. It is not an input to the metric, which stays count-based (the insurer loses or does not). Using it only for the curve is what makes an ~11% one-step labelling error tolerable: it smears the curve rather than relocating cases between outcome categories, so no re-vote was bought. STATED LIMITATION, which this field measures and the count-based metric cannot see: 305 of the 1,725 decisions scored as a claimant win -- 17.7% -- were granted LESS than fully (substantially 174, partly 118, minimally 13). The metric treats full recovery and minimal recovery as the same win, and this is the size of that. Report it; do not build it in. How much of what the worker PRESSED was granted, counting partial success within a head. Replaces the heads_succeeded/heads_claimed ratio, which measured the wrong granularity: 64.4% of the corpus presses a single head, so the ratio could only be 0 or 1 and scored 60% of 'mixed' decisions at a perfect 1.0. This is the field that makes the definitional question a sensitivity curve rather than a two-point comparison.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>relief_agreement</t>
+          <t>relief_granted_evidence</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6342,24 +6346,20 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>audit</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>single_vote / unanimous / majority / no_majority / not_run</t>
-        </is>
-      </c>
+          <t>llm_second_pass</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>How the delivered degree was arrived at. Re-voting is TARGETED at the middle three categories, where the sensitivity threshold slides, so an extreme carrying 'single_vote' is not less trustworthy than a re-voted middle case -- it was never in doubt.</t>
+          <t>Verbatim quote from the orders supporting the degree.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>relief_votes</t>
+          <t>relief_agreement</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6379,19 +6379,19 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>comma-separated</t>
+          <t>single_vote / unanimous / majority / no_majority / not_run</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Every vote cast, keyed internally by seed so the production vote and the pilot's first vote (which share a seed) cannot be counted twice.</t>
+          <t>How the delivered degree was arrived at. Re-voting is TARGETED at the middle three categories, where the sensitivity threshold slides, so an extreme carrying 'single_vote' is not less trustworthy than a re-voted middle case -- it was never in doubt.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>relief_stability</t>
+          <t>relief_votes</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6409,22 +6409,26 @@
           <t>audit</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>comma-separated</t>
+        </is>
+      </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Records that this field is SINGLE-VOTE. Piloted at 89% unanimous over 3 votes on 100 cases, against 91% on the gated fields. Gating was declined deliberately: the field feeds a sensitivity curve, where a label moving one adjacent step blurs the line, rather than a cohort assignment, where it would relocate a case between analysis populations. Treat roughly 11% of values as soft.</t>
+          <t>Every vote cast, keyed internally by seed so the production vote and the pilot's first vote (which share a seed) cannot be counted twice.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>review_flags</t>
+          <t>relief_stability</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>conduct</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6434,47 +6438,75 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>semicolon-separated</t>
-        </is>
-      </c>
+          <t>audit</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
+          <t>Records that this field is SINGLE-VOTE. Piloted at 89% unanimous over 3 votes on 100 cases, against 91% on the gated fields. Gating was declined deliberately: the field feeds a sensitivity curve, where a label moving one adjacent step blurs the line, rather than a cohort assignment, where it would relocate a case between analysis populations. Treat roughly 11% of values as soft.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>review_flags</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>semicolon-separated</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Named quality problems on this row: no_decision_text, suspiciously_short_text, llm_failed, disagreement:&lt;field&gt; (on the binary/factual watchlist only, not the taxonomies), permanent_impairment_without_wpi, lump_sum_flagged_without_amount, implausible_age, implausible_wpi, mixed_outcome_without_reason, wpi_recovered_by_llm_only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
           <t>needs_review_derived</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>review</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
         <is>
           <t>derived</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>Yes / No</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Whether this row tripped any quality flag defined here. Replaces the pipeline flag, which cannot see an empty WPI in a permanent-impairment matter or a binary field where two independent extractors disagree.</t>
         </is>
@@ -6971,7 +7003,11 @@
           <t>Yes — counted directly, see the counts column.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3501 decisions extracted, of which 2385 workers compensation (2 of 3,503 citations failed extraction)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/docs/wc_data_dictionary.xlsx
+++ b/docs/wc_data_dictionary.xlsx
@@ -7416,7 +7416,11 @@
           <t>The residual risk after every suspicion-triggered defence lives entirely in results that look right. That is not a gap in diligence, it is a structural property of diligence, and the only answer is checks that do not wait to be motivated.</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>The wrong-construct species is not confined to fields. The validity criterion for liability_posture_3v was 'if the derived field and the LLM field disagree substantially, something is wrong' - and the raw disagreement came in at 45.6%, which sounds like a five-alarm result. It was not. 41.3% of it was cases moving into a value the binary HAS NO WAY TO EXPRESS, which is the new field working exactly as designed. Decomposed, the genuine conflict was 2.6%. The check was measuring agreement between two instruments with different vocabularies and calling it error. A check can measure the wrong construct as easily as a field can, and it is worse when it does, because the check is what you were relying on to catch the field.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
